--- a/artfynd/A 64675-2021 artfynd.xlsx
+++ b/artfynd/A 64675-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 64675-2021 artfynd.xlsx
+++ b/artfynd/A 64675-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY36"/>
+  <dimension ref="A1:AY37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4884,6 +4884,108 @@
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>114938524</v>
+      </c>
+      <c r="B37" t="n">
+        <v>91550</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>5449</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Simsbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>515742</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6704841</v>
+      </c>
+      <c r="S37" t="n">
+        <v>25</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2023-10-05</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2023-10-05</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Jakob Wallin</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Jakob Wallin</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 64675-2021 artfynd.xlsx
+++ b/artfynd/A 64675-2021 artfynd.xlsx
@@ -4991,7 +4991,7 @@
         <v>121212237</v>
       </c>
       <c r="B38" t="n">
-        <v>90652</v>
+        <v>90662</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>

--- a/artfynd/A 64675-2021 artfynd.xlsx
+++ b/artfynd/A 64675-2021 artfynd.xlsx
@@ -4991,7 +4991,7 @@
         <v>121212237</v>
       </c>
       <c r="B38" t="n">
-        <v>90662</v>
+        <v>90674</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>

--- a/artfynd/A 64675-2021 artfynd.xlsx
+++ b/artfynd/A 64675-2021 artfynd.xlsx
@@ -4991,7 +4991,7 @@
         <v>121212237</v>
       </c>
       <c r="B38" t="n">
-        <v>90674</v>
+        <v>90675</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>

--- a/artfynd/A 64675-2021 artfynd.xlsx
+++ b/artfynd/A 64675-2021 artfynd.xlsx
@@ -4991,7 +4991,7 @@
         <v>121212237</v>
       </c>
       <c r="B38" t="n">
-        <v>90675</v>
+        <v>90678</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>

--- a/artfynd/A 64675-2021 artfynd.xlsx
+++ b/artfynd/A 64675-2021 artfynd.xlsx
@@ -4991,7 +4991,7 @@
         <v>121212237</v>
       </c>
       <c r="B38" t="n">
-        <v>90678</v>
+        <v>90684</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>

--- a/artfynd/A 64675-2021 artfynd.xlsx
+++ b/artfynd/A 64675-2021 artfynd.xlsx
@@ -4991,7 +4991,7 @@
         <v>121212237</v>
       </c>
       <c r="B38" t="n">
-        <v>90684</v>
+        <v>90685</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>

--- a/artfynd/A 64675-2021 artfynd.xlsx
+++ b/artfynd/A 64675-2021 artfynd.xlsx
@@ -5087,7 +5087,7 @@
         <v>122826670</v>
       </c>
       <c r="B39" t="n">
-        <v>90905</v>
+        <v>90909</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5200,7 +5200,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122826463</v>
+        <v>122826635</v>
       </c>
       <c r="B40" t="n">
         <v>56688</v>
@@ -5248,13 +5248,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>515514</v>
+        <v>515668</v>
       </c>
       <c r="R40" t="n">
-        <v>6704975</v>
+        <v>6704827</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5294,6 +5294,11 @@
       <c r="AB40" t="inlineStr">
         <is>
           <t>12:52</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Flertal  fotspår.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5320,7 +5325,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122826635</v>
+        <v>122826389</v>
       </c>
       <c r="B41" t="n">
         <v>56688</v>
@@ -5368,13 +5373,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>515668</v>
+        <v>515494</v>
       </c>
       <c r="R41" t="n">
-        <v>6704827</v>
+        <v>6704999</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5414,11 +5419,6 @@
       <c r="AB41" t="inlineStr">
         <is>
           <t>12:52</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Flertal  fotspår.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5445,7 +5445,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122826389</v>
+        <v>122826463</v>
       </c>
       <c r="B42" t="n">
         <v>56688</v>
@@ -5493,10 +5493,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>515494</v>
+        <v>515514</v>
       </c>
       <c r="R42" t="n">
-        <v>6704999</v>
+        <v>6704975</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>

--- a/artfynd/A 64675-2021 artfynd.xlsx
+++ b/artfynd/A 64675-2021 artfynd.xlsx
@@ -5325,7 +5325,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122826389</v>
+        <v>122826463</v>
       </c>
       <c r="B41" t="n">
         <v>56688</v>
@@ -5373,10 +5373,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>515494</v>
+        <v>515514</v>
       </c>
       <c r="R41" t="n">
-        <v>6704999</v>
+        <v>6704975</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5445,7 +5445,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122826463</v>
+        <v>122826389</v>
       </c>
       <c r="B42" t="n">
         <v>56688</v>
@@ -5493,10 +5493,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>515514</v>
+        <v>515494</v>
       </c>
       <c r="R42" t="n">
-        <v>6704975</v>
+        <v>6704999</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>

--- a/artfynd/A 64675-2021 artfynd.xlsx
+++ b/artfynd/A 64675-2021 artfynd.xlsx
@@ -5084,10 +5084,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122826670</v>
+        <v>122826389</v>
       </c>
       <c r="B39" t="n">
-        <v>90909</v>
+        <v>56688</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5100,26 +5100,31 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5127,10 +5132,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>515728</v>
+        <v>515494</v>
       </c>
       <c r="R39" t="n">
-        <v>6704752</v>
+        <v>6704999</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -5162,7 +5167,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5172,7 +5177,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5181,7 +5186,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5200,10 +5204,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122826635</v>
+        <v>122826670</v>
       </c>
       <c r="B40" t="n">
-        <v>56688</v>
+        <v>90909</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5216,31 +5220,26 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5248,13 +5247,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>515668</v>
+        <v>515728</v>
       </c>
       <c r="R40" t="n">
-        <v>6704827</v>
+        <v>6704752</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5283,7 +5282,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5293,12 +5292,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:52</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Flertal  fotspår.</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5307,6 +5301,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5445,7 +5440,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122826389</v>
+        <v>122826635</v>
       </c>
       <c r="B42" t="n">
         <v>56688</v>
@@ -5493,13 +5488,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>515494</v>
+        <v>515668</v>
       </c>
       <c r="R42" t="n">
-        <v>6704999</v>
+        <v>6704827</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5539,6 +5534,11 @@
       <c r="AB42" t="inlineStr">
         <is>
           <t>12:52</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Flertal  fotspår.</t>
         </is>
       </c>
       <c r="AD42" t="b">

--- a/artfynd/A 64675-2021 artfynd.xlsx
+++ b/artfynd/A 64675-2021 artfynd.xlsx
@@ -5084,10 +5084,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122826389</v>
+        <v>122826670</v>
       </c>
       <c r="B39" t="n">
-        <v>56688</v>
+        <v>90909</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5100,31 +5100,26 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5132,10 +5127,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>515494</v>
+        <v>515728</v>
       </c>
       <c r="R39" t="n">
-        <v>6704999</v>
+        <v>6704752</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -5167,7 +5162,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5177,7 +5172,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5186,6 +5181,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5204,10 +5200,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122826670</v>
+        <v>122826389</v>
       </c>
       <c r="B40" t="n">
-        <v>90909</v>
+        <v>56688</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5220,26 +5216,31 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5247,10 +5248,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>515728</v>
+        <v>515494</v>
       </c>
       <c r="R40" t="n">
-        <v>6704752</v>
+        <v>6704999</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5282,7 +5283,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5292,7 +5293,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5301,7 +5302,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 64675-2021 artfynd.xlsx
+++ b/artfynd/A 64675-2021 artfynd.xlsx
@@ -5084,10 +5084,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122826670</v>
+        <v>122826389</v>
       </c>
       <c r="B39" t="n">
-        <v>90909</v>
+        <v>56688</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5100,26 +5100,31 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5127,10 +5132,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>515728</v>
+        <v>515494</v>
       </c>
       <c r="R39" t="n">
-        <v>6704752</v>
+        <v>6704999</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -5162,7 +5167,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5172,7 +5177,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5181,7 +5186,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5200,10 +5204,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122826389</v>
+        <v>122826670</v>
       </c>
       <c r="B40" t="n">
-        <v>56688</v>
+        <v>90909</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5216,31 +5220,26 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5248,10 +5247,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>515494</v>
+        <v>515728</v>
       </c>
       <c r="R40" t="n">
-        <v>6704999</v>
+        <v>6704752</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5283,7 +5282,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5293,7 +5292,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5302,6 +5301,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 64675-2021 artfynd.xlsx
+++ b/artfynd/A 64675-2021 artfynd.xlsx
@@ -5084,7 +5084,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122826389</v>
+        <v>122826635</v>
       </c>
       <c r="B39" t="n">
         <v>56688</v>
@@ -5132,13 +5132,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>515494</v>
+        <v>515668</v>
       </c>
       <c r="R39" t="n">
-        <v>6704999</v>
+        <v>6704827</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5178,6 +5178,11 @@
       <c r="AB39" t="inlineStr">
         <is>
           <t>12:52</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Flertal  fotspår.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5204,10 +5209,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122826670</v>
+        <v>122826389</v>
       </c>
       <c r="B40" t="n">
-        <v>90909</v>
+        <v>56688</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5220,26 +5225,31 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5247,10 +5257,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>515728</v>
+        <v>515494</v>
       </c>
       <c r="R40" t="n">
-        <v>6704752</v>
+        <v>6704999</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5282,7 +5292,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5292,7 +5302,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5301,7 +5311,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5440,10 +5449,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122826635</v>
+        <v>122826670</v>
       </c>
       <c r="B42" t="n">
-        <v>56688</v>
+        <v>90909</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5456,31 +5465,26 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5488,13 +5492,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>515668</v>
+        <v>515728</v>
       </c>
       <c r="R42" t="n">
-        <v>6704827</v>
+        <v>6704752</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5523,7 +5527,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5533,12 +5537,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:52</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Flertal  fotspår.</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5547,6 +5546,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 64675-2021 artfynd.xlsx
+++ b/artfynd/A 64675-2021 artfynd.xlsx
@@ -5084,10 +5084,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122826635</v>
+        <v>122826670</v>
       </c>
       <c r="B39" t="n">
-        <v>56688</v>
+        <v>90917</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5100,31 +5100,26 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5132,13 +5127,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>515668</v>
+        <v>515728</v>
       </c>
       <c r="R39" t="n">
-        <v>6704827</v>
+        <v>6704752</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5167,7 +5162,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5177,12 +5172,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:52</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Flertal  fotspår.</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5191,6 +5181,7 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
+      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5209,7 +5200,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122826389</v>
+        <v>122826463</v>
       </c>
       <c r="B40" t="n">
         <v>56688</v>
@@ -5257,10 +5248,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>515494</v>
+        <v>515514</v>
       </c>
       <c r="R40" t="n">
-        <v>6704999</v>
+        <v>6704975</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5329,7 +5320,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122826463</v>
+        <v>122826635</v>
       </c>
       <c r="B41" t="n">
         <v>56688</v>
@@ -5377,13 +5368,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>515514</v>
+        <v>515668</v>
       </c>
       <c r="R41" t="n">
-        <v>6704975</v>
+        <v>6704827</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5423,6 +5414,11 @@
       <c r="AB41" t="inlineStr">
         <is>
           <t>12:52</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Flertal  fotspår.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5449,10 +5445,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122826670</v>
+        <v>122826389</v>
       </c>
       <c r="B42" t="n">
-        <v>90909</v>
+        <v>56688</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5465,26 +5461,31 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5492,10 +5493,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>515728</v>
+        <v>515494</v>
       </c>
       <c r="R42" t="n">
-        <v>6704752</v>
+        <v>6704999</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5527,7 +5528,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5537,7 +5538,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5546,7 +5547,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 64675-2021 artfynd.xlsx
+++ b/artfynd/A 64675-2021 artfynd.xlsx
@@ -5084,10 +5084,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122826670</v>
+        <v>122826463</v>
       </c>
       <c r="B39" t="n">
-        <v>90917</v>
+        <v>56688</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5100,26 +5100,31 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
@@ -5127,10 +5132,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>515728</v>
+        <v>515514</v>
       </c>
       <c r="R39" t="n">
-        <v>6704752</v>
+        <v>6704975</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -5162,7 +5167,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5172,7 +5177,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5181,7 +5186,6 @@
       <c r="AE39" t="b">
         <v>0</v>
       </c>
-      <c r="AF39" t="inlineStr"/>
       <c r="AG39" t="b">
         <v>0</v>
       </c>
@@ -5200,10 +5204,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122826463</v>
+        <v>122826670</v>
       </c>
       <c r="B40" t="n">
-        <v>56688</v>
+        <v>90917</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5216,31 +5220,26 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5248,10 +5247,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>515514</v>
+        <v>515728</v>
       </c>
       <c r="R40" t="n">
-        <v>6704975</v>
+        <v>6704752</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5283,7 +5282,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5293,7 +5292,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5302,6 +5301,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 64675-2021 artfynd.xlsx
+++ b/artfynd/A 64675-2021 artfynd.xlsx
@@ -5084,7 +5084,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122826463</v>
+        <v>122826389</v>
       </c>
       <c r="B39" t="n">
         <v>56688</v>
@@ -5132,10 +5132,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>515514</v>
+        <v>515494</v>
       </c>
       <c r="R39" t="n">
-        <v>6704975</v>
+        <v>6704999</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -5320,7 +5320,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122826635</v>
+        <v>122826463</v>
       </c>
       <c r="B41" t="n">
         <v>56688</v>
@@ -5368,13 +5368,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>515668</v>
+        <v>515514</v>
       </c>
       <c r="R41" t="n">
-        <v>6704827</v>
+        <v>6704975</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5414,11 +5414,6 @@
       <c r="AB41" t="inlineStr">
         <is>
           <t>12:52</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Flertal  fotspår.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5445,7 +5440,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122826389</v>
+        <v>122826635</v>
       </c>
       <c r="B42" t="n">
         <v>56688</v>
@@ -5493,13 +5488,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>515494</v>
+        <v>515668</v>
       </c>
       <c r="R42" t="n">
-        <v>6704999</v>
+        <v>6704827</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5539,6 +5534,11 @@
       <c r="AB42" t="inlineStr">
         <is>
           <t>12:52</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Flertal  fotspår.</t>
         </is>
       </c>
       <c r="AD42" t="b">

--- a/artfynd/A 64675-2021 artfynd.xlsx
+++ b/artfynd/A 64675-2021 artfynd.xlsx
@@ -5204,10 +5204,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122826670</v>
+        <v>122826635</v>
       </c>
       <c r="B40" t="n">
-        <v>90917</v>
+        <v>56688</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5220,26 +5220,31 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5247,13 +5252,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>515728</v>
+        <v>515668</v>
       </c>
       <c r="R40" t="n">
-        <v>6704752</v>
+        <v>6704827</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5282,7 +5287,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5292,7 +5297,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Flertal  fotspår.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5301,7 +5311,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5440,10 +5449,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122826635</v>
+        <v>122826670</v>
       </c>
       <c r="B42" t="n">
-        <v>56688</v>
+        <v>90917</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5456,31 +5465,26 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5488,13 +5492,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>515668</v>
+        <v>515728</v>
       </c>
       <c r="R42" t="n">
-        <v>6704827</v>
+        <v>6704752</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5523,7 +5527,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5533,12 +5537,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:52</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Flertal  fotspår.</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5547,6 +5546,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 64675-2021 artfynd.xlsx
+++ b/artfynd/A 64675-2021 artfynd.xlsx
@@ -5084,7 +5084,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122826389</v>
+        <v>122826635</v>
       </c>
       <c r="B39" t="n">
         <v>56688</v>
@@ -5132,13 +5132,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>515494</v>
+        <v>515668</v>
       </c>
       <c r="R39" t="n">
-        <v>6704999</v>
+        <v>6704827</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5178,6 +5178,11 @@
       <c r="AB39" t="inlineStr">
         <is>
           <t>12:52</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Flertal  fotspår.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5204,7 +5209,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122826635</v>
+        <v>122826463</v>
       </c>
       <c r="B40" t="n">
         <v>56688</v>
@@ -5252,13 +5257,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>515668</v>
+        <v>515514</v>
       </c>
       <c r="R40" t="n">
-        <v>6704827</v>
+        <v>6704975</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5298,11 +5303,6 @@
       <c r="AB40" t="inlineStr">
         <is>
           <t>12:52</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Flertal  fotspår.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5329,7 +5329,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122826463</v>
+        <v>122826389</v>
       </c>
       <c r="B41" t="n">
         <v>56688</v>
@@ -5377,10 +5377,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>515514</v>
+        <v>515494</v>
       </c>
       <c r="R41" t="n">
-        <v>6704975</v>
+        <v>6704999</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>

--- a/artfynd/A 64675-2021 artfynd.xlsx
+++ b/artfynd/A 64675-2021 artfynd.xlsx
@@ -912,7 +912,7 @@
         <v>66501291</v>
       </c>
       <c r="B4" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -2677,7 +2677,7 @@
         <v>71197550</v>
       </c>
       <c r="B19" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2801,7 +2801,7 @@
         <v>71197509</v>
       </c>
       <c r="B20" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -5087,7 +5087,7 @@
         <v>122826635</v>
       </c>
       <c r="B39" t="n">
-        <v>56688</v>
+        <v>56691</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5209,10 +5209,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122826463</v>
+        <v>122826670</v>
       </c>
       <c r="B40" t="n">
-        <v>56688</v>
+        <v>90920</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5225,31 +5225,26 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5257,10 +5252,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>515514</v>
+        <v>515728</v>
       </c>
       <c r="R40" t="n">
-        <v>6704975</v>
+        <v>6704752</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -5292,7 +5287,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5302,7 +5297,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5311,6 +5306,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5329,10 +5325,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122826389</v>
+        <v>122826463</v>
       </c>
       <c r="B41" t="n">
-        <v>56688</v>
+        <v>56691</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5377,10 +5373,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>515494</v>
+        <v>515514</v>
       </c>
       <c r="R41" t="n">
-        <v>6704999</v>
+        <v>6704975</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5449,10 +5445,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122826670</v>
+        <v>122826389</v>
       </c>
       <c r="B42" t="n">
-        <v>90917</v>
+        <v>56691</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5465,26 +5461,31 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5492,10 +5493,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>515728</v>
+        <v>515494</v>
       </c>
       <c r="R42" t="n">
-        <v>6704752</v>
+        <v>6704999</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5527,7 +5528,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5537,7 +5538,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5546,7 +5547,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 64675-2021 artfynd.xlsx
+++ b/artfynd/A 64675-2021 artfynd.xlsx
@@ -5084,7 +5084,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122826635</v>
+        <v>122826389</v>
       </c>
       <c r="B39" t="n">
         <v>56691</v>
@@ -5132,13 +5132,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>515668</v>
+        <v>515494</v>
       </c>
       <c r="R39" t="n">
-        <v>6704827</v>
+        <v>6704999</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5178,11 +5178,6 @@
       <c r="AB39" t="inlineStr">
         <is>
           <t>12:52</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Flertal  fotspår.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5209,10 +5204,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122826670</v>
+        <v>122826635</v>
       </c>
       <c r="B40" t="n">
-        <v>90920</v>
+        <v>56691</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5225,26 +5220,31 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5252,13 +5252,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>515728</v>
+        <v>515668</v>
       </c>
       <c r="R40" t="n">
-        <v>6704752</v>
+        <v>6704827</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5287,7 +5287,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5297,7 +5297,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Flertal  fotspår.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5306,7 +5311,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5445,10 +5449,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122826389</v>
+        <v>122826670</v>
       </c>
       <c r="B42" t="n">
-        <v>56691</v>
+        <v>90922</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5461,31 +5465,26 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5493,10 +5492,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>515494</v>
+        <v>515728</v>
       </c>
       <c r="R42" t="n">
-        <v>6704999</v>
+        <v>6704752</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5528,7 +5527,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5538,7 +5537,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5547,6 +5546,7 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
+      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 64675-2021 artfynd.xlsx
+++ b/artfynd/A 64675-2021 artfynd.xlsx
@@ -5204,10 +5204,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122826635</v>
+        <v>122826670</v>
       </c>
       <c r="B40" t="n">
-        <v>56691</v>
+        <v>90928</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5220,31 +5220,26 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
@@ -5252,13 +5247,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>515668</v>
+        <v>515728</v>
       </c>
       <c r="R40" t="n">
-        <v>6704827</v>
+        <v>6704752</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5287,7 +5282,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5297,12 +5292,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:52</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Flertal  fotspår.</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5311,6 +5301,7 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
+      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5449,10 +5440,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122826670</v>
+        <v>122826635</v>
       </c>
       <c r="B42" t="n">
-        <v>90922</v>
+        <v>56691</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5465,26 +5456,31 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
@@ -5492,13 +5488,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>515728</v>
+        <v>515668</v>
       </c>
       <c r="R42" t="n">
-        <v>6704752</v>
+        <v>6704827</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5527,7 +5523,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5537,7 +5533,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>12:52</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Flertal  fotspår.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5546,7 +5547,6 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 64675-2021 artfynd.xlsx
+++ b/artfynd/A 64675-2021 artfynd.xlsx
@@ -5568,7 +5568,7 @@
         <v>131219323</v>
       </c>
       <c r="B43" t="n">
-        <v>57080</v>
+        <v>57086</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5677,7 +5677,7 @@
         <v>131219238</v>
       </c>
       <c r="B44" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5787,7 +5787,7 @@
         <v>131219286</v>
       </c>
       <c r="B45" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 64675-2021 artfynd.xlsx
+++ b/artfynd/A 64675-2021 artfynd.xlsx
@@ -5568,7 +5568,7 @@
         <v>131219323</v>
       </c>
       <c r="B43" t="n">
-        <v>57086</v>
+        <v>57087</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5677,7 +5677,7 @@
         <v>131219238</v>
       </c>
       <c r="B44" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5787,7 +5787,7 @@
         <v>131219286</v>
       </c>
       <c r="B45" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 64675-2021 artfynd.xlsx
+++ b/artfynd/A 64675-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY45"/>
+  <dimension ref="A1:AY48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>66501289</v>
+        <v>74399493</v>
       </c>
       <c r="B2" t="n">
-        <v>90697</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5449</v>
+        <v>510</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Simsbodarna, Dlr</t>
+          <t>S Simsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>515545.252818685</v>
+        <v>515745</v>
       </c>
       <c r="R2" t="n">
-        <v>6705091.943678555</v>
+        <v>6704790</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +742,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2011-09-08</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2011-09-08</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-07</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På samma gran som vedtickan.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,38 +761,29 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>14096</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Malin Sahlin</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Malin Sahlin</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>66501263</v>
+        <v>77815000</v>
       </c>
       <c r="B3" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,37 +791,48 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4362</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Simsbodarna, Dlr</t>
+          <t>S Simsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>515701.0768279448</v>
+        <v>515752</v>
       </c>
       <c r="R3" t="n">
-        <v>6704797.815984949</v>
+        <v>6704707</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,22 +856,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2011-09-08</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-05-16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2011-09-08</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-05-16</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Minst 2 fk</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -886,38 +875,29 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>14073</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Malin Sahlin</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Via Malin Sahlin</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>66501291</v>
+        <v>71197632</v>
       </c>
       <c r="B4" t="n">
-        <v>57481</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,37 +905,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Simsbodarna, Dlr</t>
+          <t>Simsbodarna S, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>515370</v>
+        <v>515557</v>
       </c>
       <c r="R4" t="n">
-        <v>6704934</v>
+        <v>6704782</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,17 +961,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2011-09-08</t>
+          <t>2018-05-09</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2011-09-08</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>färsk bohål</t>
+          <t>2018-05-09</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -998,38 +985,29 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>14098</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Malin Sahlin</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Via Malin Sahlin</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>66501261</v>
+        <v>77815002</v>
       </c>
       <c r="B5" t="n">
-        <v>90697</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1037,37 +1015,40 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5449</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Simsbodarna, Dlr</t>
+          <t>S Simsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>515684.2191362195</v>
+        <v>515752</v>
       </c>
       <c r="R5" t="n">
-        <v>6704699.635118662</v>
+        <v>6704707</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1091,22 +1072,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2011-09-08</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-05-16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2011-09-08</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-05-16</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1115,76 +1086,70 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>14071</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Malin Sahlin</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Via Malin Sahlin</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>66501256</v>
+        <v>92434920</v>
       </c>
       <c r="B6" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Simsbodarna, Dlr</t>
+          <t>SO Simsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>515886.697277502</v>
+        <v>515749</v>
       </c>
       <c r="R6" t="n">
-        <v>6704584.165781981</v>
+        <v>6704742</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1208,27 +1173,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2011-09-08</t>
+          <t>2021-04-15</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2011-09-08</t>
+          <t>2021-04-15</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>rikligt</t>
+          <t>På granlåga.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1237,38 +1202,29 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>14066</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Malin Sahlin</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Via Malin Sahlin</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>66501262</v>
+        <v>97183873</v>
       </c>
       <c r="B7" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1276,41 +1232,38 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Simsbodarna, Dlr</t>
+          <t>Simsbodarna SO, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>515692.2526465573</v>
+        <v>515753</v>
       </c>
       <c r="R7" t="n">
-        <v>6704782.987768246</v>
+        <v>6704747</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1334,22 +1287,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2011-09-08</t>
+          <t>2021-11-16</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2011-09-08</t>
+          <t>2021-11-16</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1360,36 +1313,26 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>14072</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Malin Sahlin</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Via Malin Sahlin</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>66501265</v>
+        <v>112213272</v>
       </c>
       <c r="B8" t="n">
-        <v>90697</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,37 +1340,38 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5449</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Simsbodarna, Dlr</t>
+          <t>Simsbodarna O, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>515749.2584732238</v>
+        <v>515738</v>
       </c>
       <c r="R8" t="n">
-        <v>6704846.338734489</v>
+        <v>6704725</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1451,22 +1395,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2011-09-08</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2011-09-08</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1477,36 +1421,26 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>14075</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Malin Sahlin</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Via Malin Sahlin</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>66501292</v>
+        <v>66501263</v>
       </c>
       <c r="B9" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1514,38 +1448,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>4362</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Simsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>515369.6502689091</v>
+        <v>515701</v>
       </c>
       <c r="R9" t="n">
-        <v>6704933.936960409</v>
+        <v>6704798</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1575,21 +1505,11 @@
           <t>2011-09-08</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2011-09-08</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1601,7 +1521,7 @@
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>14099</t>
+          <t>14073</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1619,15 +1539,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>66501290</v>
+        <v>66501256</v>
       </c>
       <c r="B10" t="n">
-        <v>90697</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1635,21 +1550,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1659,10 +1574,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>515615.0906204166</v>
+        <v>515887</v>
       </c>
       <c r="R10" t="n">
-        <v>6704812.726871603</v>
+        <v>6704584</v>
       </c>
       <c r="S10" t="n">
         <v>50</v>
@@ -1692,21 +1607,11 @@
           <t>2011-09-08</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2011-09-08</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC10" t="inlineStr">
         <is>
           <t>rikligt</t>
@@ -1723,7 +1628,7 @@
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>14097</t>
+          <t>14066</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1741,15 +1646,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>66501255</v>
+        <v>73040196</v>
       </c>
       <c r="B11" t="n">
-        <v>90696</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1757,37 +1657,43 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5448</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Simsbodarna, Dlr</t>
+          <t>S Simsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>515886.697277502</v>
+        <v>515716</v>
       </c>
       <c r="R11" t="n">
-        <v>6704584.165781981</v>
+        <v>6704736</v>
       </c>
       <c r="S11" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1811,22 +1717,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2011-09-08</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-07</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2011-09-08</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-07</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>G:a fk.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1835,38 +1736,29 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>14065</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Malin Sahlin</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Via Malin Sahlin</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>66501257</v>
+        <v>97183484</v>
       </c>
       <c r="B12" t="n">
-        <v>90696</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1874,37 +1766,47 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5448</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Simsbodarna, Dlr</t>
+          <t>Simsbodarna SO, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>515833.1464860395</v>
+        <v>515471</v>
       </c>
       <c r="R12" t="n">
-        <v>6704633.726474263</v>
+        <v>6704825</v>
       </c>
       <c r="S12" t="n">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1928,22 +1830,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2011-09-08</t>
+          <t>2021-11-16</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2011-09-08</t>
+          <t>2021-11-16</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1954,36 +1856,26 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>14067</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Malin Sahlin</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Via Malin Sahlin</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>71197632</v>
+        <v>97183618</v>
       </c>
       <c r="B13" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1991,39 +1883,47 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Simsbodarna S, Dlr</t>
+          <t>Simsbodarna SO, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>515556.9544685673</v>
+        <v>515515</v>
       </c>
       <c r="R13" t="n">
-        <v>6704781.910696268</v>
+        <v>6704824</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2047,22 +1947,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2018-05-09</t>
+          <t>2021-11-16</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2018-05-09</t>
+          <t>2021-11-16</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:04</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2071,7 +1971,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2090,55 +1989,58 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>71197708</v>
+        <v>97184269</v>
       </c>
       <c r="B14" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Simsbodarna S, Dlr</t>
+          <t>Simsbodarna SO, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>515603.96080578</v>
+        <v>515662</v>
       </c>
       <c r="R14" t="n">
-        <v>6704759.928011954</v>
+        <v>6704810</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2162,22 +2064,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2018-05-09</t>
+          <t>2021-11-16</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2018-05-09</t>
+          <t>2021-11-16</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2186,7 +2088,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2205,55 +2106,58 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>71197688</v>
+        <v>97184504</v>
       </c>
       <c r="B15" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Simsbodarna S, Dlr</t>
+          <t>Simsbodarna SO, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>515682.0605763582</v>
+        <v>515536</v>
       </c>
       <c r="R15" t="n">
-        <v>6704855.906748692</v>
+        <v>6704802</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2277,22 +2181,27 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2018-05-09</t>
+          <t>2021-11-16</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2018-05-09</t>
+          <t>2021-11-16</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:51</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>2 kvm.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2301,7 +2210,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2320,52 +2228,56 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>71197719</v>
+        <v>97188740</v>
       </c>
       <c r="B16" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Simsbodarna S, Dlr</t>
+          <t>Simsbodarna SO, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>515492.8368418628</v>
+        <v>515572</v>
       </c>
       <c r="R16" t="n">
-        <v>6704879.248193881</v>
+        <v>6704791</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2392,22 +2304,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2018-05-09</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>09:00</t>
+          <t>2021-11-16</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2018-05-09</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2021-11-16</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2435,15 +2337,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>73040242</v>
+        <v>102284394</v>
       </c>
       <c r="B17" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2451,39 +2348,47 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>S Simsbodarna, Dlr</t>
+          <t>Simsbodarna O, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>515695.067917401</v>
+        <v>515490</v>
       </c>
       <c r="R17" t="n">
-        <v>6704817.016764476</v>
+        <v>6704991</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2507,22 +2412,27 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2018-09-07</t>
+          <t>2022-07-16</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2018-09-07</t>
+          <t>2022-07-16</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:13</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>G:a fk.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2531,7 +2441,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2550,19 +2459,14 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>73040196</v>
+        <v>112274505</v>
       </c>
       <c r="B18" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2583,26 +2487,31 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr">
         <is>
           <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>S Simsbodarna, Dlr</t>
+          <t>Simsbodarna Ö, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>515716.1603897997</v>
+        <v>515431</v>
       </c>
       <c r="R18" t="n">
-        <v>6704735.763263784</v>
+        <v>6704883</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2626,27 +2535,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2018-09-07</t>
+          <t>2023-09-23</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2018-09-07</t>
+          <t>2023-09-23</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>G:a fk.</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2662,69 +2566,59 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Håkan Sandin</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Håkan Sandin</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>71197550</v>
+        <v>71197688</v>
       </c>
       <c r="B19" t="n">
-        <v>57481</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Simsbodarna S, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>515556</v>
+        <v>515682</v>
       </c>
       <c r="R19" t="n">
-        <v>6704791</v>
+        <v>6704856</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2769,17 +2663,13 @@
           <t>13:00</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Hackringar</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2798,65 +2688,47 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>71197509</v>
+        <v>71197708</v>
       </c>
       <c r="B20" t="n">
-        <v>57481</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>bobesök?</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Simsbodarna S, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>515652</v>
+        <v>515604</v>
       </c>
       <c r="R20" t="n">
-        <v>6704981</v>
+        <v>6704760</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2907,6 +2779,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2925,61 +2798,47 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>77815000</v>
+        <v>71197719</v>
       </c>
       <c r="B21" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>S Simsbodarna, Dlr</t>
+          <t>Simsbodarna S, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>515751.8407995811</v>
+        <v>515493</v>
       </c>
       <c r="R21" t="n">
-        <v>6704706.830915251</v>
+        <v>6704879</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3006,27 +2865,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2019-05-16</t>
+          <t>2018-05-09</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2019-05-16</t>
+          <t>2018-05-09</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Minst 2 fk</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3054,53 +2908,47 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>77815002</v>
+        <v>73040223</v>
       </c>
       <c r="B22" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>S Simsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>515751.8407995811</v>
+        <v>515745</v>
       </c>
       <c r="R22" t="n">
-        <v>6704706.830915251</v>
+        <v>6704790</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3127,22 +2975,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2019-05-16</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-07</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2019-05-16</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2018-09-07</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3170,56 +3008,49 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>92434920</v>
+        <v>112213305</v>
       </c>
       <c r="B23" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>SO Simsbodarna, Dlr</t>
+          <t>Simsbodarna O, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>515749.219456659</v>
+        <v>515748</v>
       </c>
       <c r="R23" t="n">
-        <v>6704741.823026094</v>
+        <v>6704727</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3243,27 +3074,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2021-04-15</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2021-04-15</t>
+          <t>2023-09-20</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>På granlåga.</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3272,7 +3098,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3291,64 +3116,51 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>92434454</v>
+        <v>121212237</v>
       </c>
       <c r="B24" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>SO Simsbodarna, Dlr</t>
+          <t>Sims bodarna, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>515754.0828501005</v>
+        <v>515756</v>
       </c>
       <c r="R24" t="n">
-        <v>6704985.873428216</v>
+        <v>6704947</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>75</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3372,27 +3184,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2021-04-15</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>07:30</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2021-04-15</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Död halvstående gran.</t>
+          <t>2024-11-16</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3408,27 +3205,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>97184269</v>
+        <v>122826670</v>
       </c>
       <c r="B25" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3436,47 +3228,40 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Simsbodarna SO, Dlr</t>
+          <t>Simsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>515662.0115835405</v>
+        <v>515728</v>
       </c>
       <c r="R25" t="n">
-        <v>6704810.464632611</v>
+        <v>6704752</v>
       </c>
       <c r="S25" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3500,22 +3285,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2021-11-16</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2021-11-16</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3524,6 +3309,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3535,70 +3321,55 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>97183618</v>
+        <v>66501255</v>
       </c>
       <c r="B26" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93223</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>5448</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Simsbodarna SO, Dlr</t>
+          <t>Simsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>515515.789694769</v>
+        <v>515887</v>
       </c>
       <c r="R26" t="n">
-        <v>6704823.638683014</v>
+        <v>6704584</v>
       </c>
       <c r="S26" t="n">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3622,22 +3393,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2021-11-16</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>12:04</t>
+          <t>2011-09-08</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2021-11-16</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>12:04</t>
+          <t>2011-09-08</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3648,31 +3409,31 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AR26" t="inlineStr">
+        <is>
+          <t>14065</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Malin Sahlin</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Via Malin Sahlin</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>97183873</v>
+        <v>66501257</v>
       </c>
       <c r="B27" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93223</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3680,38 +3441,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>5448</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Simsbodarna SO, Dlr</t>
+          <t>Simsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>515752.650325115</v>
+        <v>515833</v>
       </c>
       <c r="R27" t="n">
-        <v>6704747.754010675</v>
+        <v>6704634</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3735,22 +3495,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2021-11-16</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>12:46</t>
+          <t>2011-09-08</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2021-11-16</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>12:46</t>
+          <t>2011-09-08</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3761,79 +3511,73 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AR27" t="inlineStr">
+        <is>
+          <t>14067</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Malin Sahlin</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Via Malin Sahlin</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>97184504</v>
+        <v>66501262</v>
       </c>
       <c r="B28" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Simsbodarna SO, Dlr</t>
+          <t>Simsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>515536.1282402921</v>
+        <v>515692</v>
       </c>
       <c r="R28" t="n">
-        <v>6704802.034150931</v>
+        <v>6704783</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3857,27 +3601,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2021-11-16</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>13:51</t>
+          <t>2011-09-08</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2021-11-16</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>13:51</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>2 kvm.</t>
+          <t>2011-09-08</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3888,80 +3617,73 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AR28" t="inlineStr">
+        <is>
+          <t>14072</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Malin Sahlin</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Via Malin Sahlin</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>97188740</v>
+        <v>66501292</v>
       </c>
       <c r="B29" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Simsbodarna SO, Dlr</t>
+          <t>Simsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>515572.2261109984</v>
+        <v>515370</v>
       </c>
       <c r="R29" t="n">
-        <v>6704790.357346806</v>
+        <v>6704934</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3985,22 +3707,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2021-11-16</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-09-08</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2021-11-16</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2011-09-08</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4009,82 +3721,73 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AR29" t="inlineStr">
+        <is>
+          <t>14099</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Malin Sahlin</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Via Malin Sahlin</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>102284394</v>
+        <v>73040242</v>
       </c>
       <c r="B30" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Simsbodarna O, Dlr</t>
+          <t>S Simsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>515489.8889734744</v>
+        <v>515695</v>
       </c>
       <c r="R30" t="n">
-        <v>6704991.141653389</v>
+        <v>6704817</v>
       </c>
       <c r="S30" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4108,27 +3811,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2022-07-16</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>11:13</t>
+          <t>2018-09-07</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2022-07-16</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>11:13</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>G:a fk.</t>
+          <t>2018-09-07</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4137,6 +3825,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4155,73 +3844,59 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>107216477</v>
+        <v>92434398</v>
       </c>
       <c r="B31" t="n">
-        <v>55608</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Simsbodarna O, Dlr</t>
+          <t>SO Simsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>515587.63384905</v>
+        <v>515599</v>
       </c>
       <c r="R31" t="n">
-        <v>6704996.491029504</v>
+        <v>6704715</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4245,22 +3920,27 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2023-03-10</t>
+          <t>2021-04-15</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2023-03-10</t>
+          <t>2021-04-15</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>På äldre tall.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4269,6 +3949,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4287,15 +3968,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>112213272</v>
+        <v>66501291</v>
       </c>
       <c r="B32" t="n">
-        <v>89592</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4303,38 +3979,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Simsbodarna O, Dlr</t>
+          <t>Simsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>515738</v>
+        <v>515370</v>
       </c>
       <c r="R32" t="n">
-        <v>6704726</v>
+        <v>6704934</v>
       </c>
       <c r="S32" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4358,22 +4033,17 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>13:14</t>
+          <t>2011-09-08</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>13:14</t>
+          <t>2011-09-08</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>färsk bohål</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4384,70 +4054,84 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AR32" t="inlineStr">
+        <is>
+          <t>14098</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Malin Sahlin</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Via Malin Sahlin</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>112213305</v>
+        <v>71197509</v>
       </c>
       <c r="B33" t="n">
-        <v>89556</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>bobesök?</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Simsbodarna O, Dlr</t>
+          <t>Simsbodarna S, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>515748</v>
+        <v>515652</v>
       </c>
       <c r="R33" t="n">
-        <v>6704727</v>
+        <v>6704981</v>
       </c>
       <c r="S33" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4471,22 +4155,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2018-05-09</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2018-05-09</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4513,64 +4197,55 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>112274505</v>
+        <v>71197550</v>
       </c>
       <c r="B34" t="n">
-        <v>90855</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Simsbodarna Ö, Dlr</t>
+          <t>Simsbodarna S, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>515431</v>
+        <v>515556</v>
       </c>
       <c r="R34" t="n">
-        <v>6704883</v>
+        <v>6704791</v>
       </c>
       <c r="S34" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4594,7 +4269,7 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2023-09-23</t>
+          <t>2018-05-09</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
@@ -4604,12 +4279,17 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2023-09-23</t>
+          <t>2018-05-09</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Hackringar</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4618,34 +4298,28 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Håkan Sandin</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Håkan Sandin</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>112539791</v>
+        <v>131219238</v>
       </c>
       <c r="B35" t="n">
-        <v>90966</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4653,48 +4327,45 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5449</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Simsbodarna, Dlr</t>
+          <t>Sims bodarna, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>515374</v>
+        <v>515365</v>
       </c>
       <c r="R35" t="n">
-        <v>6704951</v>
+        <v>6704964</v>
       </c>
       <c r="S35" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4718,27 +4389,17 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2023-10-05</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>16:30</t>
+          <t>2026-02-14</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2023-10-05</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>16:30</t>
+          <t>2026-02-14</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>En mindre fk.</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4747,80 +4408,74 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Bo karlstens, Anna-Lena Thommson, Niklas Rehn, Matilda Elgerud, Malte Lindberg, Holger Martinussen</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>112617404</v>
+        <v>131219286</v>
       </c>
       <c r="B36" t="n">
-        <v>55842</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Sims fäbodar, Dlr</t>
+          <t>Sims bodarna, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>515644</v>
+        <v>515382</v>
       </c>
       <c r="R36" t="n">
-        <v>6704830</v>
+        <v>6704962</v>
       </c>
       <c r="S36" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4844,12 +4499,17 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2023-10-08</t>
+          <t>2026-02-14</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2023-10-08</t>
+          <t>2026-02-14</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4876,53 +4536,55 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>114938524</v>
+        <v>56153855</v>
       </c>
       <c r="B37" t="n">
-        <v>91649</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5449</v>
+        <v>100138</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Simsbodarna, Dlr</t>
+          <t>S Simsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>515743</v>
+        <v>515579</v>
       </c>
       <c r="R37" t="n">
-        <v>6704842</v>
+        <v>6704984</v>
       </c>
       <c r="S37" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4946,12 +4608,17 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2023-10-05</t>
+          <t>2015-12-01</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2023-10-05</t>
+          <t>2015-12-01</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Spår, spillning, tjädertall.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4966,27 +4633,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Jakob Wallin</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Jakob Wallin</t>
+          <t>Lars-Erik Nilsson, Sören Nyström</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>121212237</v>
+        <v>70273875</v>
       </c>
       <c r="B38" t="n">
-        <v>90685</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4994,40 +4656,44 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Sims bodarna, Dlr</t>
+          <t>Simsbodarna S, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>515756</v>
+        <v>515634</v>
       </c>
       <c r="R38" t="n">
-        <v>6704947</v>
+        <v>6704773</v>
       </c>
       <c r="S38" t="n">
-        <v>75</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5051,12 +4717,17 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2018-03-31</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-11-16</t>
+          <t>2018-03-31</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>På snön, släpande vingar.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5065,34 +4736,28 @@
       <c r="AE38" t="b">
         <v>0</v>
       </c>
-      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122826389</v>
+        <v>97183561</v>
       </c>
       <c r="B39" t="n">
-        <v>56691</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5117,28 +4782,39 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Simsbodarna, Dlr</t>
+          <t>Simsbodarna SO, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>515494</v>
+        <v>515502</v>
       </c>
       <c r="R39" t="n">
-        <v>6704999</v>
+        <v>6704824</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5162,22 +4838,27 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2021-11-16</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2021-11-16</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>11:57</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>I tall.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5197,22 +4878,17 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122826463</v>
+        <v>107216033</v>
       </c>
       <c r="B40" t="n">
-        <v>56691</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5239,26 +4915,29 @@
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Simsbodarna, Dlr</t>
+          <t>Simsbodarna O, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>515514</v>
+        <v>515508</v>
       </c>
       <c r="R40" t="n">
-        <v>6704975</v>
+        <v>6704789</v>
       </c>
       <c r="S40" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5282,22 +4961,22 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2023-03-10</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2023-03-10</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5317,22 +4996,17 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122826635</v>
+        <v>110419160</v>
       </c>
       <c r="B41" t="n">
-        <v>56691</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5358,27 +5032,34 @@
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Simsbodarna, Dlr</t>
+          <t>Simsbodarna O, Simsbodarna O, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>515668</v>
+        <v>515578</v>
       </c>
       <c r="R41" t="n">
-        <v>6704827</v>
+        <v>6704927</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5402,27 +5083,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2023-06-29</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2023-06-29</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:52</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Flertal  fotspår.</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5442,22 +5118,17 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122826670</v>
+        <v>112617404</v>
       </c>
       <c r="B42" t="n">
-        <v>90931</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5465,40 +5136,45 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Simsbodarna, Dlr</t>
+          <t>Sims fäbodar, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>515728</v>
+        <v>515643</v>
       </c>
       <c r="R42" t="n">
-        <v>6704752</v>
+        <v>6704830</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>75</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5522,22 +5198,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>14:05</t>
+          <t>2023-10-08</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>14:05</t>
+          <t>2023-10-08</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5546,29 +5212,28 @@
       <c r="AE42" t="b">
         <v>0</v>
       </c>
-      <c r="AF42" t="inlineStr"/>
       <c r="AG42" t="b">
         <v>0</v>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+          <t>Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131219323</v>
+        <v>122826389</v>
       </c>
       <c r="B43" t="n">
-        <v>57087</v>
+        <v>57141</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5593,32 +5258,28 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Sims bodarna, Dlr</t>
+          <t>Simsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>515391</v>
+        <v>515494</v>
       </c>
       <c r="R43" t="n">
-        <v>6704950</v>
+        <v>6704999</v>
       </c>
       <c r="S43" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5642,12 +5303,22 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5662,44 +5333,44 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131219238</v>
+        <v>122826463</v>
       </c>
       <c r="B44" t="n">
-        <v>57899</v>
+        <v>57141</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5713,17 +5384,17 @@
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Sims bodarna, Dlr</t>
+          <t>Simsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>515365</v>
+        <v>515514</v>
       </c>
       <c r="R44" t="n">
-        <v>6704964</v>
+        <v>6704975</v>
       </c>
       <c r="S44" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5747,17 +5418,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5772,44 +5448,44 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Anna-Lena Thommson</t>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131219286</v>
+        <v>122826635</v>
       </c>
       <c r="B45" t="n">
-        <v>57899</v>
+        <v>57141</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5823,17 +5499,17 @@
       <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Sims bodarna, Dlr</t>
+          <t>Simsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>515382</v>
+        <v>515668</v>
       </c>
       <c r="R45" t="n">
-        <v>6704962</v>
+        <v>6704827</v>
       </c>
       <c r="S45" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5857,17 +5533,27 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-02-14</t>
+          <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Flertal  fotspår.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5882,15 +5568,371 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>122826702</v>
+      </c>
+      <c r="B46" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Simsbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>515780</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6704766</v>
+      </c>
+      <c r="S46" t="n">
+        <v>25</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>14:17</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Flertal högar med spillning under äldre tallar.</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson, Anna-Lena Thommson</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>131219323</v>
+      </c>
+      <c r="B47" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Sims bodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>515391</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6704950</v>
+      </c>
+      <c r="S47" t="n">
+        <v>25</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-02-14</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-02-14</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
           <t>Anna-Lena Thommson</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
+      <c r="AX47" t="inlineStr">
         <is>
           <t>Anna-Lena Thommson</t>
         </is>
       </c>
-      <c r="AY45" t="inlineStr"/>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>107216477</v>
+      </c>
+      <c r="B48" t="n">
+        <v>57132</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>102612</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Tetrastes bonasia</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Simsbodarna O, Dlr</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>515587</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6704996</v>
+      </c>
+      <c r="S48" t="n">
+        <v>25</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Borlänge</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Stora Tuna</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2023-03-10</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2023-03-10</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Lars-Erik Nilsson</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 64675-2021 artfynd.xlsx
+++ b/artfynd/A 64675-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY48"/>
+  <dimension ref="A1:AZ48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74399493</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -891,6 +901,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/77815000</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1001,6 +1016,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71197632</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1102,6 +1122,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/77815002</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1218,6 +1243,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92434920</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1326,6 +1356,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97183873</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1434,6 +1469,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112213272</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1536,6 +1576,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66501263</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1643,6 +1688,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66501256</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1752,6 +1802,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73040196</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1869,6 +1924,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97183484</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1986,6 +2046,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97183618</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2103,6 +2168,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97184269</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2225,6 +2295,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97184504</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2334,6 +2409,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97188740</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2456,6 +2536,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102284394</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2575,6 +2660,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112274505</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2685,6 +2775,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71197688</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2795,6 +2890,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71197708</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2905,6 +3005,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71197719</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3005,6 +3110,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73040223</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3113,6 +3223,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112213305</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3214,6 +3329,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121212237</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3325,6 +3445,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122826670</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3427,6 +3552,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66501255</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3529,6 +3659,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66501257</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3635,6 +3770,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66501262</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3741,6 +3881,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66501292</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3841,6 +3986,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73040242</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3965,6 +4115,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/92434398</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4072,6 +4227,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66501291</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4194,6 +4354,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71197509</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4313,6 +4478,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/71197550</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4423,6 +4593,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131219238</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4533,6 +4708,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131219286</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4642,6 +4822,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56153855</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4751,6 +4936,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70273875</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4882,6 +5072,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97183561</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5000,6 +5195,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107216033</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5122,6 +5322,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110419160</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5227,6 +5432,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112617404</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5342,6 +5552,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122826389</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5457,6 +5672,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122826463</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5577,6 +5797,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122826635</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5697,6 +5922,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122826702</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5806,6 +6036,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131219323</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5933,8 +6168,62 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107216477</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>